--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K684"/>
+  <dimension ref="A1:K688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27087,10 +27087,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>324.68</v>
+        <v>328.69</v>
       </c>
       <c r="C684" t="n">
-        <v>338.6</v>
+        <v>341.44</v>
       </c>
       <c r="D684" t="n">
         <v>343.76</v>
@@ -27114,6 +27114,162 @@
         <v>367.22</v>
       </c>
       <c r="K684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="C685" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="D685" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="E685" t="n">
+        <v>338.09</v>
+      </c>
+      <c r="F685" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="G685" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="H685" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="I685" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="J685" t="n">
+        <v>367.53</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>325.48</v>
+      </c>
+      <c r="C686" t="n">
+        <v>342.93</v>
+      </c>
+      <c r="D686" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="E686" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="F686" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="G686" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="H686" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="I686" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="J686" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>323.98</v>
+      </c>
+      <c r="C687" t="n">
+        <v>341.89</v>
+      </c>
+      <c r="D687" t="n">
+        <v>343.52</v>
+      </c>
+      <c r="E687" t="n">
+        <v>338.29</v>
+      </c>
+      <c r="F687" t="n">
+        <v>343.14</v>
+      </c>
+      <c r="G687" t="n">
+        <v>351.84</v>
+      </c>
+      <c r="H687" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="I687" t="n">
+        <v>358.34</v>
+      </c>
+      <c r="J687" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="C688" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="D688" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="E688" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="F688" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="G688" t="n">
+        <v>351.77</v>
+      </c>
+      <c r="H688" t="n">
+        <v>355.12</v>
+      </c>
+      <c r="I688" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="J688" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="K688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27130,7 +27286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34563,6 +34719,56 @@
       </c>
       <c r="B743" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -34731,28 +34937,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07864231467048605</v>
+        <v>-0.08705549287147188</v>
       </c>
       <c r="J2" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003887691820816386</v>
+        <v>0.004799497497790295</v>
       </c>
       <c r="M2" t="n">
-        <v>7.31198056667101</v>
+        <v>7.308073652723699</v>
       </c>
       <c r="N2" t="n">
-        <v>73.11670598729704</v>
+        <v>72.98649592144959</v>
       </c>
       <c r="O2" t="n">
-        <v>8.550830719134664</v>
+        <v>8.543213442344138</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7341645467084</v>
+        <v>334.8377280503349</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34813,28 +35019,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1821853018372498</v>
+        <v>-0.1850672925441458</v>
       </c>
       <c r="J3" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1171284524867879</v>
+        <v>0.1216167550869199</v>
       </c>
       <c r="M3" t="n">
-        <v>2.79443742619259</v>
+        <v>2.791283517239059</v>
       </c>
       <c r="N3" t="n">
-        <v>11.63194594811062</v>
+        <v>11.57631307451148</v>
       </c>
       <c r="O3" t="n">
-        <v>3.41056387538932</v>
+        <v>3.402398135802375</v>
       </c>
       <c r="P3" t="n">
-        <v>350.1216710176288</v>
+        <v>350.1570232317319</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34895,28 +35101,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08491540408417483</v>
+        <v>-0.09387948469523978</v>
       </c>
       <c r="J4" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03649841232032969</v>
+        <v>0.04335260291887644</v>
       </c>
       <c r="M4" t="n">
-        <v>2.409603224939346</v>
+        <v>2.434820145967929</v>
       </c>
       <c r="N4" t="n">
-        <v>8.849974303120389</v>
+        <v>9.101194581330038</v>
       </c>
       <c r="O4" t="n">
-        <v>2.974890637169775</v>
+        <v>3.016818619229542</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0836288178556</v>
+        <v>353.1934796634306</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34973,28 +35179,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1429186131121472</v>
+        <v>-0.1502089308953006</v>
       </c>
       <c r="J5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09422653912120371</v>
+        <v>0.1021965642685032</v>
       </c>
       <c r="M5" t="n">
-        <v>2.308714572738669</v>
+        <v>2.32788734883793</v>
       </c>
       <c r="N5" t="n">
-        <v>9.128817498706713</v>
+        <v>9.275915136964674</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02139330420697</v>
+        <v>3.045638707556212</v>
       </c>
       <c r="P5" t="n">
-        <v>348.0401308585731</v>
+        <v>348.1294702817493</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35051,28 +35257,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1819627843854884</v>
+        <v>-0.1849170354415267</v>
       </c>
       <c r="J6" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1816988376714015</v>
+        <v>0.1876882966072372</v>
       </c>
       <c r="M6" t="n">
-        <v>2.015773953295677</v>
+        <v>2.017243552201124</v>
       </c>
       <c r="N6" t="n">
-        <v>6.932929011614323</v>
+        <v>6.925635828657027</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63304557720035</v>
+        <v>2.6316602798722</v>
       </c>
       <c r="P6" t="n">
-        <v>350.6268273526604</v>
+        <v>350.6630314195919</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35129,28 +35335,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.207533333907773</v>
+        <v>-0.2100920376048969</v>
       </c>
       <c r="J7" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.16908828660349</v>
+        <v>0.1739674660346066</v>
       </c>
       <c r="M7" t="n">
-        <v>2.479336832157166</v>
+        <v>2.476228558765029</v>
       </c>
       <c r="N7" t="n">
-        <v>9.802342020135077</v>
+        <v>9.770010836556896</v>
       </c>
       <c r="O7" t="n">
-        <v>3.130869211598446</v>
+        <v>3.125701655077928</v>
       </c>
       <c r="P7" t="n">
-        <v>359.5793857602725</v>
+        <v>359.6108140614018</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35207,28 +35413,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1992905483455285</v>
+        <v>-0.2019191594605985</v>
       </c>
       <c r="J8" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K8" t="n">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1890919235372172</v>
+        <v>0.1945430565254076</v>
       </c>
       <c r="M8" t="n">
-        <v>2.149599578465834</v>
+        <v>2.150346865393006</v>
       </c>
       <c r="N8" t="n">
-        <v>7.888325423048846</v>
+        <v>7.869160409788704</v>
       </c>
       <c r="O8" t="n">
-        <v>2.808616282629018</v>
+        <v>2.805202383035617</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1688222764834</v>
+        <v>363.2011104503472</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35285,28 +35491,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08347747101036683</v>
+        <v>-0.08733996758063015</v>
       </c>
       <c r="J9" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K9" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03210188384580392</v>
+        <v>0.03525598070326919</v>
       </c>
       <c r="M9" t="n">
-        <v>2.389813192416217</v>
+        <v>2.395398306232453</v>
       </c>
       <c r="N9" t="n">
-        <v>9.768508963586401</v>
+        <v>9.768449530971216</v>
       </c>
       <c r="O9" t="n">
-        <v>3.125461400111414</v>
+        <v>3.125451892282333</v>
       </c>
       <c r="P9" t="n">
-        <v>363.6357418776685</v>
+        <v>363.6830758819866</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35363,28 +35569,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1127780216580961</v>
+        <v>-0.1167726225161693</v>
       </c>
       <c r="J10" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="K10" t="n">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06077046864539748</v>
+        <v>0.06521506499533236</v>
       </c>
       <c r="M10" t="n">
-        <v>2.317476355658108</v>
+        <v>2.321857629290873</v>
       </c>
       <c r="N10" t="n">
-        <v>9.139421028412245</v>
+        <v>9.146735699360535</v>
       </c>
       <c r="O10" t="n">
-        <v>3.023147536659805</v>
+        <v>3.024357072066811</v>
       </c>
       <c r="P10" t="n">
-        <v>373.6807927535064</v>
+        <v>373.729746244641</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35422,7 +35628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K684"/>
+  <dimension ref="A1:K688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74352,12 +74558,12 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>-45.26028592127766,170.8611460905272</t>
+          <t>-45.260310311660945,170.8611837435664</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>-45.26084108630183,170.86068444108142</t>
+          <t>-45.260860224892134,170.86070842054113</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
@@ -74396,6 +74602,234 @@
         </is>
       </c>
       <c r="K684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-45.260301917964306,170.86117078565897</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-45.26086736816757,170.86071737062525</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-45.261248335852216,170.86000544154885</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-45.26172456452649,170.8594279230565</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-45.26231120844954,170.85908454714297</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-45.262933815454716,170.85891346264722</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-45.26353834329335,170.85871760026265</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-45.26414091351178,170.858668996661</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-45.264747023198666,170.85886939469117</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-45.26029078719049,170.86115360235289</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-45.26087026591118,170.8607210013204</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-45.261251760784326,170.86001014093685</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-45.26172683872679,170.85943297211233</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-45.262311706637924,170.85908618557758</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-45.26293534160206,170.85892012917174</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-45.26353941239415,170.8587248339262</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-45.26414103733385,170.85867740466603</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-45.26474683719494,170.85887308056132</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:51+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-45.26028166360355,170.86113951768078</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-45.260863257414805,170.86071222010486</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-45.26124943441537,170.86000694889967</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-45.26172553227133,170.85943007159085</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-45.26231006973316,170.8590808021496</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-45.26293398194354,170.85891418990443</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-45.26353825112945,170.858716976671</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-45.26414096041416,170.85867218151137</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-45.26474724127186,170.85886507332614</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-45.260273269902086,170.86112655978644</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-45.26086002272395,170.86070816723688</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-45.261248335852216,170.86000544154885</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-45.261725000011666,170.85942888989695</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-45.26231010531804,170.85908091918066</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-45.26293378770658,170.8589133414377</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-45.26353727419207,170.8587103665994</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-45.264140866609324,170.85866581181062</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-45.26474729899709,170.8588639294354</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K688"/>
+  <dimension ref="A1:K693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27270,6 +27270,201 @@
         <v>367.1</v>
       </c>
       <c r="K688" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>322.35</v>
+      </c>
+      <c r="C689" t="n">
+        <v>340.89</v>
+      </c>
+      <c r="D689" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="E689" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="F689" t="n">
+        <v>342.91</v>
+      </c>
+      <c r="G689" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="H689" t="n">
+        <v>354.64</v>
+      </c>
+      <c r="I689" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="J689" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="C690" t="n">
+        <v>340.71</v>
+      </c>
+      <c r="D690" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="E690" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="F690" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="G690" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="H690" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="I690" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="J690" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:12+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="C691" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="D691" t="n">
+        <v>342.3</v>
+      </c>
+      <c r="E691" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="F691" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="G691" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="H691" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="I691" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="J691" t="n">
+        <v>365.91</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="C692" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="D692" t="n">
+        <v>342.3</v>
+      </c>
+      <c r="E692" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="F692" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="G692" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="H692" t="n">
+        <v>354.53</v>
+      </c>
+      <c r="I692" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="J692" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>323.2</v>
+      </c>
+      <c r="C693" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="D693" t="n">
+        <v>342.82</v>
+      </c>
+      <c r="E693" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="F693" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="G693" t="n">
+        <v>351.79</v>
+      </c>
+      <c r="H693" t="n">
+        <v>354.75</v>
+      </c>
+      <c r="I693" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="J693" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="K693" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27286,7 +27481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B748"/>
+  <dimension ref="A1:B753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34769,6 +34964,56 @@
       </c>
       <c r="B748" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -34937,28 +35182,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08705549287147188</v>
+        <v>-0.1020584247384078</v>
       </c>
       <c r="J2" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K2" t="n">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004799497497790295</v>
+        <v>0.006623495046140015</v>
       </c>
       <c r="M2" t="n">
-        <v>7.308073652723699</v>
+        <v>7.323751189786393</v>
       </c>
       <c r="N2" t="n">
-        <v>72.98649592144959</v>
+        <v>73.14130188658575</v>
       </c>
       <c r="O2" t="n">
-        <v>8.543213442344138</v>
+        <v>8.552268815149915</v>
       </c>
       <c r="P2" t="n">
-        <v>334.8377280503349</v>
+        <v>335.0228487959495</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35019,28 +35264,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1850672925441458</v>
+        <v>-0.1910662158577644</v>
       </c>
       <c r="J3" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K3" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1216167550869199</v>
+        <v>0.1292304180751379</v>
       </c>
       <c r="M3" t="n">
-        <v>2.791283517239059</v>
+        <v>2.798407316812517</v>
       </c>
       <c r="N3" t="n">
-        <v>11.57631307451148</v>
+        <v>11.60399302058133</v>
       </c>
       <c r="O3" t="n">
-        <v>3.402398135802375</v>
+        <v>3.406463418353605</v>
       </c>
       <c r="P3" t="n">
-        <v>350.1570232317319</v>
+        <v>350.2307492062316</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -35101,28 +35346,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09387948469523978</v>
+        <v>-0.1058646437418644</v>
       </c>
       <c r="J4" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K4" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04335260291887644</v>
+        <v>0.05283882257775652</v>
       </c>
       <c r="M4" t="n">
-        <v>2.434820145967929</v>
+        <v>2.470587304255956</v>
       </c>
       <c r="N4" t="n">
-        <v>9.101194581330038</v>
+        <v>9.477063527073362</v>
       </c>
       <c r="O4" t="n">
-        <v>3.016818619229542</v>
+        <v>3.078483965700221</v>
       </c>
       <c r="P4" t="n">
-        <v>353.1934796634306</v>
+        <v>353.3407890709647</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35179,28 +35424,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1502089308953006</v>
+        <v>-0.1589557469575416</v>
       </c>
       <c r="J5" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1021965642685032</v>
+        <v>0.1120654508475888</v>
       </c>
       <c r="M5" t="n">
-        <v>2.32788734883793</v>
+        <v>2.350574080349596</v>
       </c>
       <c r="N5" t="n">
-        <v>9.275915136964674</v>
+        <v>9.44414908478867</v>
       </c>
       <c r="O5" t="n">
-        <v>3.045638707556212</v>
+        <v>3.073133431009573</v>
       </c>
       <c r="P5" t="n">
-        <v>348.1294702817493</v>
+        <v>348.2369712926453</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35257,28 +35502,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1849170354415267</v>
+        <v>-0.1889790312567817</v>
       </c>
       <c r="J6" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K6" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1876882966072372</v>
+        <v>0.1956474791927704</v>
       </c>
       <c r="M6" t="n">
-        <v>2.017243552201124</v>
+        <v>2.020644686137638</v>
       </c>
       <c r="N6" t="n">
-        <v>6.925635828657027</v>
+        <v>6.926288245637308</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6316602798722</v>
+        <v>2.631784232348334</v>
       </c>
       <c r="P6" t="n">
-        <v>350.6630314195919</v>
+        <v>350.7129548898331</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35335,28 +35580,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2100920376048969</v>
+        <v>-0.2136121714642782</v>
       </c>
       <c r="J7" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K7" t="n">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1739674660346066</v>
+        <v>0.1804740819288143</v>
       </c>
       <c r="M7" t="n">
-        <v>2.476228558765029</v>
+        <v>2.473806981682053</v>
       </c>
       <c r="N7" t="n">
-        <v>9.770010836556896</v>
+        <v>9.737168180653203</v>
       </c>
       <c r="O7" t="n">
-        <v>3.125701655077928</v>
+        <v>3.120443587160839</v>
       </c>
       <c r="P7" t="n">
-        <v>359.6108140614018</v>
+        <v>359.6541774112576</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35413,28 +35658,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2019191594605985</v>
+        <v>-0.2067373272881506</v>
       </c>
       <c r="J8" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K8" t="n">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1945430565254076</v>
+        <v>0.2030508013341674</v>
       </c>
       <c r="M8" t="n">
-        <v>2.150346865393006</v>
+        <v>2.159029217404453</v>
       </c>
       <c r="N8" t="n">
-        <v>7.869160409788704</v>
+        <v>7.883091274679281</v>
       </c>
       <c r="O8" t="n">
-        <v>2.805202383035617</v>
+        <v>2.807684326037968</v>
       </c>
       <c r="P8" t="n">
-        <v>363.2011104503472</v>
+        <v>363.2604639904806</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35491,28 +35736,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08733996758063015</v>
+        <v>-0.09302169631420289</v>
       </c>
       <c r="J9" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K9" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03525598070326919</v>
+        <v>0.03999836586251126</v>
       </c>
       <c r="M9" t="n">
-        <v>2.395398306232453</v>
+        <v>2.406747412121017</v>
       </c>
       <c r="N9" t="n">
-        <v>9.768449530971216</v>
+        <v>9.797141655404607</v>
       </c>
       <c r="O9" t="n">
-        <v>3.125451892282333</v>
+        <v>3.130038602861729</v>
       </c>
       <c r="P9" t="n">
-        <v>363.6830758819866</v>
+        <v>363.7529066395635</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35569,28 +35814,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1167726225161693</v>
+        <v>-0.1226112936491673</v>
       </c>
       <c r="J10" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="K10" t="n">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06521506499533236</v>
+        <v>0.07166586930977159</v>
       </c>
       <c r="M10" t="n">
-        <v>2.321857629290873</v>
+        <v>2.330818065658249</v>
       </c>
       <c r="N10" t="n">
-        <v>9.146735699360535</v>
+        <v>9.186583941593037</v>
       </c>
       <c r="O10" t="n">
-        <v>3.024357072066811</v>
+        <v>3.030937799030696</v>
       </c>
       <c r="P10" t="n">
-        <v>373.729746244641</v>
+        <v>373.8015057086637</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35628,7 +35873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K688"/>
+  <dimension ref="A1:K693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74835,6 +75080,291 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:01+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-45.26027174930383,170.86112421234222</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-45.26085651847537,170.8607037766304</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-45.26124775425996,170.8600046435396</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-45.261723887105084,170.8594264190825</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-45.26230925128068,170.85907811043572</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-45.26293339923265,170.85891164450425</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-45.263536389418256,170.85870438011972</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-45.26414081407847,170.85866224477823</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-45.26474736955013,170.85886253134672</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-45.260273269902086,170.86112655978644</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-45.260855305466215,170.8607022568052</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-45.26124717266769,170.86000384553037</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-45.26172538710959,170.8594297493107</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-45.26230942920514,170.8590786955909</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-45.26293339923265,170.85891164450425</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-45.26353618665757,170.85870300821813</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-45.26414079719354,170.85866109823206</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-45.264747581209136,170.8588583370806</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-11 22:20:12+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-45.260273269902086,170.86112655978644</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-45.26085995533455,170.86070808280215</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-45.26124155060882,170.85999613144213</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-45.26172538710959,170.8594297493107</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-45.26230942920514,170.8590786955909</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-45.26293320499566,170.85891079603752</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-45.26353618665757,170.85870300821813</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-45.26414079719354,170.85866109823206</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-45.26474806225178,170.85884880465758</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-45.260273269902086,170.86112655978644</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-45.26085995533455,170.86070808280215</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-45.26124155060882,170.85999613144213</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-45.26172538710959,170.8594297493107</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-45.26230942920514,170.8590786955909</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-45.26293320499566,170.85891079603752</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-45.26353618665757,170.85870300821813</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>-45.26414079719354,170.85866109823206</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>-45.264747356722296,170.85886278554466</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-45.26027691933768,170.86113219365308</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-45.26086170745879,170.86071027810556</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-45.26124491091994,170.86000074216136</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-45.26172819356942,170.85943598006068</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-45.26231035441226,170.85908173839792</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-45.26293384320285,170.85891358385675</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-45.26353659217896,170.85870575202128</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>-45.26414088912253,170.8586673405388</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>-45.26474729899709,170.8588639294354</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K693"/>
+  <dimension ref="A1:K696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27465,6 +27465,123 @@
         <v>367.1</v>
       </c>
       <c r="K693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="C694" t="n">
+        <v>341.14</v>
+      </c>
+      <c r="D694" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="E694" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="F694" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="G694" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="H694" t="n">
+        <v>357.54</v>
+      </c>
+      <c r="I694" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="J694" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>322.43</v>
+      </c>
+      <c r="C695" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="D695" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="E695" t="n">
+        <v>339.21</v>
+      </c>
+      <c r="F695" t="n">
+        <v>344.23</v>
+      </c>
+      <c r="G695" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="H695" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="I695" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="J695" t="n">
+        <v>368.59</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>322.94</v>
+      </c>
+      <c r="C696" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="D696" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="E696" t="n">
+        <v>338.71</v>
+      </c>
+      <c r="F696" t="n">
+        <v>343.75</v>
+      </c>
+      <c r="G696" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="H696" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="I696" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="J696" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="K696" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27481,7 +27598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B753"/>
+  <dimension ref="A1:B756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35014,6 +35131,36 @@
       </c>
       <c r="B753" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -35182,28 +35329,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1020584247384078</v>
+        <v>-0.1111187992178179</v>
       </c>
       <c r="J2" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006623495046140015</v>
+        <v>0.007868805019433878</v>
       </c>
       <c r="M2" t="n">
-        <v>7.323751189786393</v>
+        <v>7.333151921362558</v>
       </c>
       <c r="N2" t="n">
-        <v>73.14130188658575</v>
+        <v>73.24518007232031</v>
       </c>
       <c r="O2" t="n">
-        <v>8.552268815149915</v>
+        <v>8.558339796497934</v>
       </c>
       <c r="P2" t="n">
-        <v>335.0228487959495</v>
+        <v>335.1351116690989</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -35264,28 +35411,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1910662158577644</v>
+        <v>-0.1941654948392164</v>
       </c>
       <c r="J3" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K3" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1292304180751379</v>
+        <v>0.1334506490061904</v>
       </c>
       <c r="M3" t="n">
-        <v>2.798407316812517</v>
+        <v>2.800385181549759</v>
       </c>
       <c r="N3" t="n">
-        <v>11.60399302058133</v>
+        <v>11.60406129336026</v>
       </c>
       <c r="O3" t="n">
-        <v>3.406463418353605</v>
+        <v>3.406473439403317</v>
       </c>
       <c r="P3" t="n">
-        <v>350.2307492062316</v>
+        <v>350.2689997519552</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -35346,28 +35493,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1058646437418644</v>
+        <v>-0.1123235175765651</v>
       </c>
       <c r="J4" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K4" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05283882257775652</v>
+        <v>0.05834516076161367</v>
       </c>
       <c r="M4" t="n">
-        <v>2.470587304255956</v>
+        <v>2.489459118893239</v>
       </c>
       <c r="N4" t="n">
-        <v>9.477063527073362</v>
+        <v>9.652095006835948</v>
       </c>
       <c r="O4" t="n">
-        <v>3.078483965700221</v>
+        <v>3.106782098383462</v>
       </c>
       <c r="P4" t="n">
-        <v>353.3407890709647</v>
+        <v>353.4205057409309</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35424,28 +35571,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1589557469575416</v>
+        <v>-0.1636407380992448</v>
       </c>
       <c r="J5" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K5" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1120654508475888</v>
+        <v>0.1176782833066442</v>
       </c>
       <c r="M5" t="n">
-        <v>2.350574080349596</v>
+        <v>2.362123970521851</v>
       </c>
       <c r="N5" t="n">
-        <v>9.44414908478867</v>
+        <v>9.517147473172241</v>
       </c>
       <c r="O5" t="n">
-        <v>3.073133431009573</v>
+        <v>3.084987434848356</v>
       </c>
       <c r="P5" t="n">
-        <v>348.2369712926453</v>
+        <v>348.2947951207239</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35502,28 +35649,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1889790312567817</v>
+        <v>-0.1904910419366926</v>
       </c>
       <c r="J6" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K6" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1956474791927704</v>
+        <v>0.1993472503120975</v>
       </c>
       <c r="M6" t="n">
-        <v>2.020644686137638</v>
+        <v>2.018599310964182</v>
       </c>
       <c r="N6" t="n">
-        <v>6.926288245637308</v>
+        <v>6.908382248784215</v>
       </c>
       <c r="O6" t="n">
-        <v>2.631784232348334</v>
+        <v>2.628380156823631</v>
       </c>
       <c r="P6" t="n">
-        <v>350.7129548898331</v>
+        <v>350.7316171348779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35580,28 +35727,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2136121714642782</v>
+        <v>-0.2143154168208572</v>
       </c>
       <c r="J7" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1804740819288143</v>
+        <v>0.1827730654034754</v>
       </c>
       <c r="M7" t="n">
-        <v>2.473806981682053</v>
+        <v>2.466178942149083</v>
       </c>
       <c r="N7" t="n">
-        <v>9.737168180653203</v>
+        <v>9.697626535127858</v>
       </c>
       <c r="O7" t="n">
-        <v>3.120443587160839</v>
+        <v>3.11410124034654</v>
       </c>
       <c r="P7" t="n">
-        <v>359.6541774112576</v>
+        <v>359.6628767368658</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35658,28 +35805,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2067373272881506</v>
+        <v>-0.2066000324734748</v>
       </c>
       <c r="J8" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K8" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2030508013341674</v>
+        <v>0.2043142983882944</v>
       </c>
       <c r="M8" t="n">
-        <v>2.159029217404453</v>
+        <v>2.150662482724942</v>
       </c>
       <c r="N8" t="n">
-        <v>7.883091274679281</v>
+        <v>7.849314249832538</v>
       </c>
       <c r="O8" t="n">
-        <v>2.807684326037968</v>
+        <v>2.801662765186513</v>
       </c>
       <c r="P8" t="n">
-        <v>363.2604639904806</v>
+        <v>363.2587644919565</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35736,28 +35883,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09302169631420289</v>
+        <v>-0.0948200718720192</v>
       </c>
       <c r="J9" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K9" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03999836586251126</v>
+        <v>0.04179079255948703</v>
       </c>
       <c r="M9" t="n">
-        <v>2.406747412121017</v>
+        <v>2.405298218794197</v>
       </c>
       <c r="N9" t="n">
-        <v>9.797141655404607</v>
+        <v>9.77177790249746</v>
       </c>
       <c r="O9" t="n">
-        <v>3.130038602861729</v>
+        <v>3.125984309381201</v>
       </c>
       <c r="P9" t="n">
-        <v>363.7529066395635</v>
+        <v>363.7751020497187</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35814,28 +35961,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1226112936491673</v>
+        <v>-0.1244791816213101</v>
       </c>
       <c r="J10" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="K10" t="n">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07166586930977159</v>
+        <v>0.07419491707482195</v>
       </c>
       <c r="M10" t="n">
-        <v>2.330818065658249</v>
+        <v>2.329014474775128</v>
       </c>
       <c r="N10" t="n">
-        <v>9.186583941593037</v>
+        <v>9.164993283934065</v>
       </c>
       <c r="O10" t="n">
-        <v>3.030937799030696</v>
+        <v>3.027373991421288</v>
       </c>
       <c r="P10" t="n">
-        <v>373.8015057086637</v>
+        <v>373.8245601322635</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35873,7 +36020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K693"/>
+  <dimension ref="A1:K696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75365,6 +75512,177 @@
         </is>
       </c>
     </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-45.26026767410032,170.86111792119235</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-45.26085820321028,170.86070588749885</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-45.2612449755413,170.86000083082905</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-45.261726112918204,170.85943136071148</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-45.26231248950533,170.85908876026065</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-45.262937283970885,170.8589286138398</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-45.263541734921944,170.85874054843762</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>-45.26414107485556,170.8586799525464</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>-45.26474651008464,170.85887956260876</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-45.26027223589529,170.86112496352436</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-45.260863122636025,170.86071205123534</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-45.26125014525034,170.86000792424434</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-45.26172998389705,170.8594399548498</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-45.26231394848534,170.85909355853383</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-45.26293758920022,170.85892994714484</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-45.2635427118576,170.85874715851028</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>-45.26414117991606,170.85868708661133</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>-45.264746343322386,170.85888286718193</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-45.260275337915616,170.8611297523108</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-45.260863526972386,170.86071255784387</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-45.26125014525034,170.86000792424434</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-45.26172756453534,170.85943458351323</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-45.26231224041116,170.85908794104333</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-45.262937561452084,170.8589298259353</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-45.26354228790444,170.85874428998815</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>-45.264141140518426,170.85868441133695</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>-45.264746490842846,170.85887994390566</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
